--- a/output/yearly_surface_area_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_13_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634550741</v>
+        <v>10.84497654492637</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907198822638</v>
+        <v>37.78907268309718</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.710425484976196</v>
+        <v>6.395104545463722</v>
       </c>
       <c r="C2" t="n">
-        <v>8.223118770771283</v>
+        <v>7.370961763485052</v>
       </c>
       <c r="D2" t="n">
-        <v>24.35225180384213</v>
+        <v>25.85236229593126</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.24239387195773</v>
+        <v>17.3278469799562</v>
       </c>
       <c r="C3" t="n">
-        <v>29.44752238888308</v>
+        <v>24.3767954964483</v>
       </c>
       <c r="D3" t="n">
-        <v>76.40942382152926</v>
+        <v>82.40299355595603</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.72062817711294</v>
+        <v>33.70634392990574</v>
       </c>
       <c r="C4" t="n">
-        <v>43.07418052382881</v>
+        <v>70.71823238001049</v>
       </c>
       <c r="D4" t="n">
-        <v>116.281143334105</v>
+        <v>96.47340165322132</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.7356164345839</v>
+        <v>43.14781160164732</v>
       </c>
       <c r="C5" t="n">
-        <v>72.1339125695344</v>
+        <v>101.1445572300277</v>
       </c>
       <c r="D5" t="n">
-        <v>89.90354601640168</v>
+        <v>61.94828013797375</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.13969557810609</v>
+        <v>39.24536447726626</v>
       </c>
       <c r="C6" t="n">
-        <v>86.50080847348222</v>
+        <v>99.90460987956394</v>
       </c>
       <c r="D6" t="n">
-        <v>57.3586096206199</v>
+        <v>43.23027840880406</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.15237618280328</v>
+        <v>28.02693346083794</v>
       </c>
       <c r="C7" t="n">
-        <v>86.83558444063037</v>
+        <v>86.05705851116265</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20198765183014</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>14.52004854581032</v>
       </c>
       <c r="C8" t="n">
-        <v>61.91882770684633</v>
+        <v>61.16779071309751</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>38.49530923122167</v>
+        <v>37.71874679716245</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -898,7 +898,7 @@
         <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -951,10 +951,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -982,7 +982,7 @@
         <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.696849307597548</v>
+        <v>7.710000201278657</v>
       </c>
       <c r="C21" t="n">
-        <v>94.28640401806996</v>
+        <v>96.37500251598321</v>
       </c>
       <c r="D21" t="n">
-        <v>7.696849307597548</v>
+        <v>8.673750226438489</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.721625620350411</v>
+        <v>6.369579105153306</v>
       </c>
       <c r="C2" t="n">
-        <v>6.738716241950107</v>
+        <v>12.03720860177014</v>
       </c>
       <c r="D2" t="n">
-        <v>25.07972685268902</v>
+        <v>28.26058941444868</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.04390090925062</v>
+        <v>19.5613230071177</v>
       </c>
       <c r="C3" t="n">
-        <v>30.66979828067036</v>
+        <v>26.50227927614264</v>
       </c>
       <c r="D3" t="n">
-        <v>77.68078709852887</v>
+        <v>83.23747910456582</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.35952494839936</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="C4" t="n">
-        <v>58.88719079613218</v>
+        <v>65.65143247839271</v>
       </c>
       <c r="D4" t="n">
-        <v>126.9763028241697</v>
+        <v>111.8269539999372</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.8772090881737</v>
+        <v>46.55938487390499</v>
       </c>
       <c r="C5" t="n">
-        <v>75.05461198966867</v>
+        <v>114.4472386225719</v>
       </c>
       <c r="D5" t="n">
-        <v>108.11496593018</v>
+        <v>80.20878743696441</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.45920555034281</v>
+        <v>48.62400029593603</v>
       </c>
       <c r="C6" t="n">
-        <v>100.5486363735499</v>
+        <v>129.288318667671</v>
       </c>
       <c r="D6" t="n">
-        <v>71.24543089719104</v>
+        <v>51.15985461600555</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.23706852727577</v>
+        <v>36.77037851486003</v>
       </c>
       <c r="C7" t="n">
-        <v>105.2207736980604</v>
+        <v>113.3653526524919</v>
       </c>
       <c r="D7" t="n">
-        <v>47.66974152740813</v>
+        <v>41.86074036137975</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.36144738607885</v>
+        <v>21.86352137357647</v>
       </c>
       <c r="C8" t="n">
-        <v>88.45546815263761</v>
+        <v>87.03684272000096</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.31718662392973</v>
+        <v>10.98281156740907</v>
       </c>
       <c r="C9" t="n">
-        <v>57.35468262980289</v>
+        <v>55.69062027110455</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>38.00836236991527</v>
+        <v>37.86600895279948</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.885131832081462</v>
+        <v>7.89530779961259</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4923552960692</v>
+        <v>105.5997418198184</v>
       </c>
       <c r="D21" t="n">
-        <v>8.870773311091645</v>
+        <v>9.869134749515737</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.105488972710914</v>
+        <v>6.970408700152354</v>
       </c>
       <c r="C2" t="n">
-        <v>5.89441321629785</v>
+        <v>9.6034560429423</v>
       </c>
       <c r="D2" t="n">
-        <v>24.8087644863169</v>
+        <v>29.71259426902972</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.33137306014569</v>
+        <v>20.10128424445344</v>
       </c>
       <c r="C3" t="n">
-        <v>28.24488145118073</v>
+        <v>36.11358930071892</v>
       </c>
       <c r="D3" t="n">
-        <v>78.69198723390309</v>
+        <v>85.20588325158067</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.83174559414208</v>
+        <v>34.35724265782137</v>
       </c>
       <c r="C4" t="n">
-        <v>67.25953521794898</v>
+        <v>65.75353423963438</v>
       </c>
       <c r="D4" t="n">
-        <v>133.4087137823948</v>
+        <v>124.487572393904</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.41087892865646</v>
+        <v>48.10563750809372</v>
       </c>
       <c r="C5" t="n">
-        <v>89.6335653977338</v>
+        <v>116.0671223345792</v>
       </c>
       <c r="D5" t="n">
-        <v>125.7127935288041</v>
+        <v>96.40762455703681</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.28940425523712</v>
+        <v>54.58124536530568</v>
       </c>
       <c r="C6" t="n">
-        <v>109.3234973541078</v>
+        <v>152.7550340422825</v>
       </c>
       <c r="D6" t="n">
-        <v>84.85049058264335</v>
+        <v>62.02780170201773</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.42346172236242</v>
+        <v>45.8132566186774</v>
       </c>
       <c r="C7" t="n">
-        <v>122.8274370260227</v>
+        <v>144.6860496610779</v>
       </c>
       <c r="D7" t="n">
-        <v>55.75443387188061</v>
+        <v>45.6934833987593</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.53802310412303</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="C8" t="n">
-        <v>111.4872692942678</v>
+        <v>114.574865824124</v>
       </c>
       <c r="D8" t="n">
-        <v>41.97462309507237</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.64374875654542</v>
+        <v>15.8640611529242</v>
       </c>
       <c r="C9" t="n">
-        <v>81.42811808563893</v>
+        <v>79.09843078346124</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>51.10487674456772</v>
+        <v>49.96604940764142</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>37.84931924182727</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.059225355925378</v>
+        <v>8.06480566681026</v>
       </c>
       <c r="C21" t="n">
-        <v>111.8217518134646</v>
+        <v>113.9153800436949</v>
       </c>
       <c r="D21" t="n">
-        <v>10.07403169490672</v>
+        <v>11.08910779186411</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.532148313430777</v>
+        <v>6.441246687563323</v>
       </c>
       <c r="C2" t="n">
-        <v>3.913246349127786</v>
+        <v>6.453027660014286</v>
       </c>
       <c r="D2" t="n">
-        <v>20.25247339090745</v>
+        <v>24.42391938625215</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.17844140246144</v>
+        <v>24.1019061392592</v>
       </c>
       <c r="C3" t="n">
-        <v>41.05668899160161</v>
+        <v>50.76617378660256</v>
       </c>
       <c r="D3" t="n">
-        <v>88.7843536335603</v>
+        <v>92.77024931280235</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.45489334443154</v>
+        <v>23.11328620108265</v>
       </c>
       <c r="C4" t="n">
-        <v>83.48095253521902</v>
+        <v>95.17160419739004</v>
       </c>
       <c r="D4" t="n">
-        <v>132.9237304164969</v>
+        <v>116.6257367782956</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.06540154775282</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="C5" t="n">
-        <v>65.31076602501908</v>
+        <v>91.2779928023472</v>
       </c>
       <c r="D5" t="n">
-        <v>85.68203088814039</v>
+        <v>63.88723185386119</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.07678160957628</v>
+        <v>28.41766904712818</v>
       </c>
       <c r="C6" t="n">
-        <v>80.86557665110554</v>
+        <v>95.27566945404023</v>
       </c>
       <c r="D6" t="n">
-        <v>36.70951015719674</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="C7" t="n">
-        <v>78.39157243640355</v>
+        <v>80.54749039492954</v>
       </c>
       <c r="D7" t="n">
-        <v>29.46421209985527</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>59.99951094504382</v>
+        <v>58.24709129296325</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93905919354123</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.291800052339555</v>
+        <v>3.91520984453628</v>
       </c>
       <c r="C2" t="n">
-        <v>1.968404147014855</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="D2" t="n">
-        <v>14.33940696822891</v>
+        <v>17.30919377357552</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.74785507092459</v>
+        <v>23.91046533693107</v>
       </c>
       <c r="C3" t="n">
-        <v>27.99944452511903</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D3" t="n">
-        <v>86.17290474026379</v>
+        <v>91.41543748094176</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.7634241654723</v>
+        <v>33.24688600431823</v>
       </c>
       <c r="C4" t="n">
-        <v>95.31199411909735</v>
+        <v>113.2436159371653</v>
       </c>
       <c r="D4" t="n">
-        <v>145.1887044856523</v>
+        <v>134.4424941149667</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.61794557879453</v>
+        <v>34.26299487821369</v>
       </c>
       <c r="C5" t="n">
-        <v>108.2131407006047</v>
+        <v>132.5113963807133</v>
       </c>
       <c r="D5" t="n">
-        <v>108.3849465488479</v>
+        <v>83.17857424231102</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.18874190558942</v>
+        <v>34.09315252537899</v>
       </c>
       <c r="C6" t="n">
-        <v>95.31592110991434</v>
+        <v>120.3927027194906</v>
       </c>
       <c r="D6" t="n">
-        <v>47.2956956520901</v>
+        <v>37.75605320992383</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.24734366820796</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>97.13608135358791</v>
+        <v>103.6038352291659</v>
       </c>
       <c r="D7" t="n">
-        <v>32.33876937788993</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>76.77267047210057</v>
+        <v>76.52232480751763</v>
       </c>
       <c r="D8" t="n">
-        <v>28.78975142703771</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>45.92812110007426</v>
+        <v>44.04218376021615</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.220132469929538</v>
+        <v>3.679590395517045</v>
       </c>
       <c r="C2" t="n">
-        <v>3.646210973572654</v>
+        <v>4.654465865834128</v>
       </c>
       <c r="D2" t="n">
-        <v>13.60113269463531</v>
+        <v>14.5740446695439</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.37907778702628</v>
+        <v>18.54521413322225</v>
       </c>
       <c r="C3" t="n">
-        <v>16.8811517745239</v>
+        <v>23.29687302177681</v>
       </c>
       <c r="D3" t="n">
-        <v>78.15693473508857</v>
+        <v>85.29914928348413</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.48112279500572</v>
+        <v>39.51338160052563</v>
       </c>
       <c r="C4" t="n">
-        <v>81.87284979566276</v>
+        <v>104.0289319851048</v>
       </c>
       <c r="D4" t="n">
-        <v>154.3906257175576</v>
+        <v>145.903416814344</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.18936380039518</v>
+        <v>41.50338419703392</v>
       </c>
       <c r="C5" t="n">
-        <v>142.6970288122739</v>
+        <v>171.9531103988289</v>
       </c>
       <c r="D5" t="n">
-        <v>132.9531828476243</v>
+        <v>109.26851948267</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.45541742824607</v>
+        <v>39.7686360036298</v>
       </c>
       <c r="C6" t="n">
-        <v>133.9172590931947</v>
+        <v>162.9387029784347</v>
       </c>
       <c r="D6" t="n">
-        <v>66.69699378341556</v>
+        <v>52.36740429222912</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.21226279276233</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="C7" t="n">
-        <v>118.1562814492164</v>
+        <v>137.8589761257456</v>
       </c>
       <c r="D7" t="n">
-        <v>37.54890444432775</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C8" t="n">
-        <v>102.1410311498382</v>
+        <v>105.1451791248334</v>
       </c>
       <c r="D8" t="n">
-        <v>30.70906818884022</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>68.33749419721195</v>
+        <v>66.45155685735384</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2495,7 +2495,7 @@
         <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.871211124294421</v>
+        <v>2.172607669498191</v>
       </c>
       <c r="C2" t="n">
-        <v>1.620865459711484</v>
+        <v>2.146100481483527</v>
       </c>
       <c r="D2" t="n">
-        <v>9.389435043416494</v>
+        <v>10.06095047312131</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.99619618237003</v>
+        <v>18.00034415736527</v>
       </c>
       <c r="C3" t="n">
-        <v>16.76825078853552</v>
+        <v>22.54092728950677</v>
       </c>
       <c r="D3" t="n">
-        <v>75.14296928305087</v>
+        <v>81.85812358009906</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.08020987877453</v>
+        <v>43.39324852770901</v>
       </c>
       <c r="C4" t="n">
-        <v>75.31281163588557</v>
+        <v>97.23916486253384</v>
       </c>
       <c r="D4" t="n">
-        <v>161.7930034075786</v>
+        <v>156.2922710206837</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.37375244234433</v>
+        <v>43.0005494460103</v>
       </c>
       <c r="C5" t="n">
-        <v>164.6881773874025</v>
+        <v>204.2035224833366</v>
       </c>
       <c r="D5" t="n">
-        <v>143.0160968161541</v>
+        <v>118.055161435679</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.26924521733767</v>
+        <v>33.61013265488955</v>
       </c>
       <c r="C6" t="n">
-        <v>168.6141864566855</v>
+        <v>196.9916038479395</v>
       </c>
       <c r="D6" t="n">
-        <v>64.72466264558373</v>
+        <v>51.15985461600555</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.26435217434965</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>129.1754176816825</v>
+        <v>142.1109254328385</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>83.36510630611789</v>
+        <v>81.94648087348126</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.874557278034661</v>
+        <v>3.065016332658542</v>
       </c>
       <c r="C2" t="n">
-        <v>5.396667130244716</v>
+        <v>4.142975311921539</v>
       </c>
       <c r="D2" t="n">
-        <v>8.400815105239955</v>
+        <v>14.32468075266521</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.75504610002381</v>
+        <v>12.85107744859075</v>
       </c>
       <c r="C3" t="n">
-        <v>11.16247139728623</v>
+        <v>15.19745446174063</v>
       </c>
       <c r="D3" t="n">
-        <v>66.63121668723102</v>
+        <v>72.06519023023712</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.67256359733385</v>
+        <v>39.60272064161208</v>
       </c>
       <c r="C4" t="n">
-        <v>58.63193639302801</v>
+        <v>77.5973385436679</v>
       </c>
       <c r="D4" t="n">
-        <v>162.3418003742526</v>
+        <v>160.7592230750067</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.64497685062371</v>
+        <v>52.59713325502288</v>
       </c>
       <c r="C5" t="n">
-        <v>153.4962535589888</v>
+        <v>194.1406085148068</v>
       </c>
       <c r="D5" t="n">
-        <v>164.4918278465531</v>
+        <v>143.6296891313084</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.56108632740622</v>
+        <v>43.51203999992289</v>
       </c>
       <c r="C6" t="n">
-        <v>213.4545311004543</v>
+        <v>255.3565048654124</v>
       </c>
       <c r="D6" t="n">
-        <v>88.31213298781759</v>
+        <v>69.63536466222628</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="C7" t="n">
-        <v>182.8937068149553</v>
+        <v>205.4709587695192</v>
       </c>
       <c r="D7" t="n">
-        <v>45.33416373900496</v>
+        <v>40.18391528252619</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>121.8348900970292</v>
+        <v>125.5900750657732</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>60.34999487545991</v>
+        <v>57.35468262980289</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3173,7 +3173,7 @@
         <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.880046853632642</v>
+        <v>2.289435646303562</v>
       </c>
       <c r="C2" t="n">
-        <v>3.467532891399734</v>
+        <v>3.160245859970483</v>
       </c>
       <c r="D2" t="n">
-        <v>6.48542533425443</v>
+        <v>11.21548577331556</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.48506548135594</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="C3" t="n">
-        <v>16.25283324380595</v>
+        <v>15.77177686872501</v>
       </c>
       <c r="D3" t="n">
-        <v>59.74425654193965</v>
+        <v>68.08911202803753</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.49915410658066</v>
+        <v>34.80393786325368</v>
       </c>
       <c r="C4" t="n">
-        <v>46.30314872309656</v>
+        <v>62.48627787990099</v>
       </c>
       <c r="D4" t="n">
-        <v>162.0865459711484</v>
+        <v>160.9889520378005</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.42470551197393</v>
+        <v>57.18680377237672</v>
       </c>
       <c r="C5" t="n">
-        <v>140.5371838629309</v>
+        <v>181.1569951261427</v>
       </c>
       <c r="D5" t="n">
-        <v>178.0644898577653</v>
+        <v>161.0802545742954</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.36361617013237</v>
+        <v>51.07935130425731</v>
       </c>
       <c r="C6" t="n">
-        <v>234.8684120254858</v>
+        <v>285.4647434592536</v>
       </c>
       <c r="D6" t="n">
-        <v>107.2304112486536</v>
+        <v>84.48822567977626</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.02586959767568</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>230.9826546120768</v>
+        <v>262.1835784007447</v>
       </c>
       <c r="D7" t="n">
-        <v>51.74203100462389</v>
+        <v>45.75337000871835</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>156.8832831386403</v>
+        <v>163.4757189726576</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>73.88436872620643</v>
+        <v>67.11718180083317</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3470,7 +3470,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.964878066825367</v>
+        <v>3.764020698082271</v>
       </c>
       <c r="C2" t="n">
-        <v>5.009858534771474</v>
+        <v>7.820602212030092</v>
       </c>
       <c r="D2" t="n">
-        <v>14.16956461539421</v>
+        <v>15.5116137270996</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.46757394912874</v>
+        <v>9.910743074371553</v>
       </c>
       <c r="C3" t="n">
-        <v>14.92256510455152</v>
+        <v>14.01444847812322</v>
       </c>
       <c r="D3" t="n">
-        <v>52.327152636355</v>
+        <v>62.28698309593889</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.36403277629309</v>
+        <v>29.11176467403067</v>
       </c>
       <c r="C4" t="n">
-        <v>43.5081130091059</v>
+        <v>51.90598287123311</v>
       </c>
       <c r="D4" t="n">
-        <v>156.1135929385108</v>
+        <v>158.3981198462931</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.78027810736052</v>
+        <v>55.29693944170161</v>
       </c>
       <c r="C5" t="n">
-        <v>115.3553552490002</v>
+        <v>152.1954378508618</v>
       </c>
       <c r="D5" t="n">
-        <v>191.8825887950391</v>
+        <v>174.5792855076891</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.53470231257858</v>
+        <v>61.22276858453534</v>
       </c>
       <c r="C6" t="n">
-        <v>230.923749749822</v>
+        <v>287.5578295647078</v>
       </c>
       <c r="D6" t="n">
-        <v>130.656874967391</v>
+        <v>107.5121728397725</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.84160412891355</v>
+        <v>32.27888276793088</v>
       </c>
       <c r="C7" t="n">
-        <v>280.7484274880518</v>
+        <v>326.7413439366064</v>
       </c>
       <c r="D7" t="n">
-        <v>64.91708519561608</v>
+        <v>55.45500082208532</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>218.2179709614598</v>
+        <v>234.5738877142116</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>122.0312396378785</v>
+        <v>117.7046775052628</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>53.52488483553611</v>
+        <v>48.9695754878309</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.473824288252715</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C2" t="n">
-        <v>5.78347572571796</v>
+        <v>5.21406205725481</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30781111524377</v>
+        <v>8.206429059799088</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.072469403665017</v>
+        <v>2.690970457340507</v>
       </c>
       <c r="C2" t="n">
-        <v>2.725331626989146</v>
+        <v>4.442408361716817</v>
       </c>
       <c r="D2" t="n">
-        <v>10.31522312852124</v>
+        <v>11.41674405268616</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.55026174046372</v>
+        <v>13.62665813494573</v>
       </c>
       <c r="C3" t="n">
-        <v>18.73174619702914</v>
+        <v>21.04376204053038</v>
       </c>
       <c r="D3" t="n">
-        <v>58.79196126882024</v>
+        <v>68.84996649882882</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.8422260237193</v>
+        <v>41.38950146334128</v>
       </c>
       <c r="C4" t="n">
-        <v>64.24753326131977</v>
+        <v>77.98022014832415</v>
       </c>
       <c r="D4" t="n">
-        <v>163.8605640727224</v>
+        <v>162.3290376540974</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.29949946972007</v>
+        <v>36.00559705325178</v>
       </c>
       <c r="C5" t="n">
-        <v>183.7586265423968</v>
+        <v>236.7975462643307</v>
       </c>
       <c r="D5" t="n">
-        <v>178.2362957060084</v>
+        <v>159.4849145548944</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.11953654020664</v>
+        <v>20.04532462531138</v>
       </c>
       <c r="C6" t="n">
-        <v>236.9614981309399</v>
+        <v>271.5779221826825</v>
       </c>
       <c r="D6" t="n">
-        <v>102.0379476408923</v>
+        <v>84.44797402390215</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.28809404570082</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>153.4294947151</v>
+        <v>164.9277238272387</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>89.95754214013523</v>
+        <v>86.70304850055705</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>25.2849121228766</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82499653339935</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.48831382410494</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.05884810899257</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.116288197457628</v>
+        <v>6.33129094468768</v>
       </c>
       <c r="C2" t="n">
-        <v>4.675082567623311</v>
+        <v>4.569053815564656</v>
       </c>
       <c r="D2" t="n">
-        <v>23.11524969649115</v>
+        <v>10.63723637551419</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.508226515630358</v>
+        <v>10.28380720198534</v>
       </c>
       <c r="C3" t="n">
-        <v>14.5740446695439</v>
+        <v>13.34686003923539</v>
       </c>
       <c r="D3" t="n">
-        <v>16.83206438931157</v>
+        <v>10.02855279888117</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39744183264139</v>
+        <v>13.39886793229715</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13954841794613</v>
+        <v>70.14701446908508</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576169627369576</v>
+        <v>1.576337403799665</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.754203221039802</v>
+        <v>4.600469742100554</v>
       </c>
       <c r="C2" t="n">
-        <v>4.548437113775472</v>
+        <v>4.587707021945345</v>
       </c>
       <c r="D2" t="n">
-        <v>35.28990297685585</v>
+        <v>9.568113125589415</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.44427404613408</v>
+        <v>17.20512851692535</v>
       </c>
       <c r="C3" t="n">
-        <v>16.86151682043897</v>
+        <v>16.19883712007237</v>
       </c>
       <c r="D3" t="n">
-        <v>32.18168974521045</v>
+        <v>16.53754007803752</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.16738013580747</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C4" t="n">
-        <v>22.76869275689203</v>
+        <v>21.21164089795658</v>
       </c>
       <c r="D4" t="n">
-        <v>23.89181213055038</v>
+        <v>20.3310132072472</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43936955440212</v>
+        <v>15.44470157869987</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13543014561183</v>
+        <v>86.16517722853612</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250393590400446</v>
+        <v>3.251516121831552</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.088979188187965</v>
+        <v>4.70944373727195</v>
       </c>
       <c r="C2" t="n">
-        <v>4.183226967795659</v>
+        <v>4.57690779719863</v>
       </c>
       <c r="D2" t="n">
-        <v>29.55649638405447</v>
+        <v>25.2682224119044</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.50041359172539</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="C3" t="n">
-        <v>17.36711688812607</v>
+        <v>17.22967220953152</v>
       </c>
       <c r="D3" t="n">
-        <v>52.94565369003049</v>
+        <v>20.35162990903638</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.8835572382889</v>
+        <v>24.3767954964483</v>
       </c>
       <c r="C4" t="n">
-        <v>34.22961545626929</v>
+        <v>32.80019079888594</v>
       </c>
       <c r="D4" t="n">
-        <v>34.63802250123597</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.11200135374215</v>
+        <v>10.94648690235194</v>
       </c>
       <c r="C5" t="n">
-        <v>26.26175108860219</v>
+        <v>24.98547907308133</v>
       </c>
       <c r="D5" t="n">
-        <v>31.24412068765475</v>
+        <v>30.13965452037709</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.82369599052563</v>
       </c>
     </row>
     <row r="11">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
         <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73053728699726</v>
+        <v>16.74488899329562</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0562774506833</v>
+        <v>102.1438228591033</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182634321749315</v>
+        <v>5.023466697988686</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.410992435180919</v>
+        <v>4.914629007459533</v>
       </c>
       <c r="C2" t="n">
-        <v>3.523492510541802</v>
+        <v>8.059166904162065</v>
       </c>
       <c r="D2" t="n">
-        <v>24.88239556413541</v>
+        <v>35.7670323611198</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.23043297305752</v>
+        <v>16.31664684458199</v>
       </c>
       <c r="C3" t="n">
-        <v>16.70443718775948</v>
+        <v>17.5438314748905</v>
       </c>
       <c r="D3" t="n">
-        <v>63.63197745075702</v>
+        <v>35.02875808752619</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.81898287398687</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="C4" t="n">
-        <v>39.38575439897354</v>
+        <v>38.67104207028186</v>
       </c>
       <c r="D4" t="n">
-        <v>52.36544079682062</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.08932334555324</v>
+        <v>24.02827506144069</v>
       </c>
       <c r="C5" t="n">
-        <v>45.9703362513569</v>
+        <v>44.57134577280519</v>
       </c>
       <c r="D5" t="n">
-        <v>36.10377182367646</v>
+        <v>32.07860623626453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.901907345033331</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>27.77364255314227</v>
+        <v>26.56609287691869</v>
       </c>
       <c r="D6" t="n">
-        <v>38.56108632740622</v>
+        <v>37.95731148929444</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
         <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05532583782487</v>
+        <v>18.07926391124617</v>
       </c>
       <c r="C21" t="n">
-        <v>117.789506656286</v>
+        <v>117.9456740876536</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018441945941621</v>
+        <v>6.887338632855685</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.595561003579319</v>
+        <v>6.388232311533995</v>
       </c>
       <c r="C2" t="n">
-        <v>6.132977908429824</v>
+        <v>8.370380926408306</v>
       </c>
       <c r="D2" t="n">
-        <v>31.0713330917073</v>
+        <v>33.96650707153115</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.10633185169492</v>
+        <v>14.85875150377547</v>
       </c>
       <c r="C3" t="n">
-        <v>14.06353586333556</v>
+        <v>24.06263623108932</v>
       </c>
       <c r="D3" t="n">
-        <v>64.34374453633596</v>
+        <v>51.1883252994287</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.37380919560656</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="C4" t="n">
-        <v>33.78292025083699</v>
+        <v>34.90603962449534</v>
       </c>
       <c r="D4" t="n">
-        <v>61.87366731245098</v>
+        <v>33.6425303291297</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.67775007329557</v>
+        <v>20.469439633546</v>
       </c>
       <c r="C5" t="n">
-        <v>45.08676331753477</v>
+        <v>43.76140391680158</v>
       </c>
       <c r="D5" t="n">
-        <v>37.92000507653306</v>
+        <v>28.49522711576368</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.02895370950867</v>
+        <v>11.83398682699105</v>
       </c>
       <c r="C6" t="n">
-        <v>34.85793398698726</v>
+        <v>34.01264921363075</v>
       </c>
       <c r="D6" t="n">
-        <v>32.00006641992479</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>19.70269467652924</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
         <v>29.7312474754104</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.057623472855219</v>
+        <v>7.069195665609535</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16522005801767</v>
+        <v>67.15735882329058</v>
       </c>
       <c r="D21" t="n">
-        <v>4.411014670534511</v>
+        <v>5.301896749207152</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.048727532313846</v>
+        <v>4.641703145678919</v>
       </c>
       <c r="C2" t="n">
-        <v>3.655046702910875</v>
+        <v>7.973754853892594</v>
       </c>
       <c r="D2" t="n">
-        <v>24.73611515620263</v>
+        <v>32.7471764228566</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.98637870532756</v>
+        <v>19.62022786937251</v>
       </c>
       <c r="C3" t="n">
-        <v>20.55779692692821</v>
+        <v>29.74204670015712</v>
       </c>
       <c r="D3" t="n">
-        <v>75.52094214918588</v>
+        <v>68.21673922958962</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.4706423654285</v>
+        <v>26.81447504609313</v>
       </c>
       <c r="C4" t="n">
-        <v>34.77841242294325</v>
+        <v>51.16574510223102</v>
       </c>
       <c r="D4" t="n">
-        <v>82.25573140031901</v>
+        <v>53.61618737203106</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.81367322483814</v>
+        <v>28.29887757491431</v>
       </c>
       <c r="C5" t="n">
-        <v>55.95961914206821</v>
+        <v>56.32777453116076</v>
       </c>
       <c r="D5" t="n">
-        <v>53.08800710714628</v>
+        <v>34.92567457858028</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.44154978719959</v>
+        <v>21.05161602216436</v>
       </c>
       <c r="C6" t="n">
-        <v>56.91584140600459</v>
+        <v>55.6680400739069</v>
       </c>
       <c r="D6" t="n">
-        <v>36.99127174831558</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>10.54004335279375</v>
       </c>
       <c r="C7" t="n">
-        <v>37.96811071404115</v>
+        <v>37.42913122440964</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>23.44904391593506</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>30.95155987178918</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6241,7 +6241,7 @@
         <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.281608224344048</v>
+        <v>7.295725720125843</v>
       </c>
       <c r="C21" t="n">
-        <v>75.54668532756949</v>
+        <v>77.51708577633708</v>
       </c>
       <c r="D21" t="n">
-        <v>5.461206168258036</v>
+        <v>6.383760005110113</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.034582153826891</v>
+        <v>5.009858534771474</v>
       </c>
       <c r="C2" t="n">
-        <v>10.004009106275</v>
+        <v>4.990223580686537</v>
       </c>
       <c r="D2" t="n">
-        <v>20.95442299944392</v>
+        <v>28.02202472231671</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.48077863764045</v>
+        <v>17.63709750679395</v>
       </c>
       <c r="C3" t="n">
-        <v>16.66516727958961</v>
+        <v>30.55689729468197</v>
       </c>
       <c r="D3" t="n">
-        <v>77.78877934599603</v>
+        <v>78.58399498643594</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.99315312826605</v>
+        <v>33.60424216866407</v>
       </c>
       <c r="C4" t="n">
-        <v>44.80991046493716</v>
+        <v>65.16644911249479</v>
       </c>
       <c r="D4" t="n">
-        <v>100.8637773866131</v>
+        <v>75.22347259479911</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.60598467989432</v>
+        <v>34.92567457858028</v>
       </c>
       <c r="C5" t="n">
-        <v>60.86835766330226</v>
+        <v>78.56436003235102</v>
       </c>
       <c r="D5" t="n">
-        <v>71.643038717411</v>
+        <v>46.95208395560371</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.53213261789756</v>
+        <v>30.83276839957533</v>
       </c>
       <c r="C6" t="n">
-        <v>74.42531171124647</v>
+        <v>74.18380177600174</v>
       </c>
       <c r="D6" t="n">
-        <v>45.60512610537709</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>63.12048689684442</v>
+        <v>61.86286808770426</v>
       </c>
       <c r="D7" t="n">
-        <v>36.83026512481909</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>38.7201294554942</v>
+        <v>38.21943812632832</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.79804737702819</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.495184206826184</v>
+        <v>7.509763099451258</v>
       </c>
       <c r="C21" t="n">
-        <v>85.25772035264784</v>
+        <v>87.30099603112087</v>
       </c>
       <c r="D21" t="n">
-        <v>6.558286180972911</v>
+        <v>7.509763099451258</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_13_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497654492637</v>
+        <v>10.84497619106077</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907268309718</v>
+        <v>37.7890714500606</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.395104545463722</v>
+        <v>5.570436473896402</v>
       </c>
       <c r="C2" t="n">
-        <v>7.370961763485052</v>
+        <v>4.240168334641973</v>
       </c>
       <c r="D2" t="n">
-        <v>25.85236229593126</v>
+        <v>30.65801730821939</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3278469799562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C3" t="n">
-        <v>24.3767954964483</v>
+        <v>23.71902453460294</v>
       </c>
       <c r="D3" t="n">
-        <v>82.40299355595603</v>
+        <v>75.33931882390023</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.70634392990574</v>
+        <v>34.89327690434013</v>
       </c>
       <c r="C4" t="n">
-        <v>70.71823238001049</v>
+        <v>73.99825145989908</v>
       </c>
       <c r="D4" t="n">
-        <v>96.47340165322132</v>
+        <v>98.27294519510572</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.14781160164732</v>
+        <v>43.56505437595222</v>
       </c>
       <c r="C5" t="n">
-        <v>101.1445572300277</v>
+        <v>134.0085616296896</v>
       </c>
       <c r="D5" t="n">
-        <v>61.94828013797375</v>
+        <v>70.26859193146547</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.24536447726626</v>
+        <v>39.92964262712628</v>
       </c>
       <c r="C6" t="n">
-        <v>99.90460987956394</v>
+        <v>149.2933916371082</v>
       </c>
       <c r="D6" t="n">
-        <v>43.23027840880406</v>
+        <v>47.41645061971246</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.02693346083794</v>
+        <v>28.32636651063322</v>
       </c>
       <c r="C7" t="n">
-        <v>86.05705851116265</v>
+        <v>122.048911096555</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20765715387736</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>14.6034971006713</v>
       </c>
       <c r="C8" t="n">
-        <v>61.16779071309751</v>
+        <v>83.19820919639595</v>
       </c>
       <c r="D8" t="n">
-        <v>36.88426124855267</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>45.26249615659493</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,7 +892,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
         <v>30.60598467989432</v>
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.710000201278657</v>
+        <v>7.662053604831931</v>
       </c>
       <c r="C21" t="n">
-        <v>96.37500251598321</v>
+        <v>92.90239995858715</v>
       </c>
       <c r="D21" t="n">
-        <v>8.673750226438489</v>
+        <v>7.662053604831931</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.369579105153306</v>
+        <v>5.478152189697202</v>
       </c>
       <c r="C2" t="n">
-        <v>12.03720860177014</v>
+        <v>8.12592574805085</v>
       </c>
       <c r="D2" t="n">
-        <v>28.26058941444868</v>
+        <v>35.85833489761475</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.5613230071177</v>
+        <v>17.94143929511046</v>
       </c>
       <c r="C3" t="n">
-        <v>26.50227927614264</v>
+        <v>19.97856578142259</v>
       </c>
       <c r="D3" t="n">
-        <v>83.23747910456582</v>
+        <v>80.37077580816513</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.0554452019901</v>
+        <v>33.78292025083699</v>
       </c>
       <c r="C4" t="n">
-        <v>65.65143247839271</v>
+        <v>66.05983952335937</v>
       </c>
       <c r="D4" t="n">
-        <v>111.8269539999372</v>
+        <v>109.3254608495163</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.55938487390499</v>
+        <v>47.24660826687776</v>
       </c>
       <c r="C5" t="n">
-        <v>114.4472386225719</v>
+        <v>134.9412219487241</v>
       </c>
       <c r="D5" t="n">
-        <v>80.20878743696441</v>
+        <v>86.34471058850698</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.62400029593603</v>
+        <v>48.66425195181016</v>
       </c>
       <c r="C6" t="n">
-        <v>129.288318667671</v>
+        <v>176.8657759108799</v>
       </c>
       <c r="D6" t="n">
-        <v>51.15985461600555</v>
+        <v>56.07055663264809</v>
       </c>
     </row>
     <row r="7">
@@ -1164,10 +1164,10 @@
         <v>36.77037851486003</v>
       </c>
       <c r="C7" t="n">
-        <v>113.3653526524919</v>
+        <v>165.1073836571158</v>
       </c>
       <c r="D7" t="n">
-        <v>41.86074036137975</v>
+        <v>43.05847256056086</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.86352137357647</v>
+        <v>21.61317570899353</v>
       </c>
       <c r="C8" t="n">
-        <v>87.03684272000096</v>
+        <v>118.0797051282851</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.98281156740907</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>55.69062027110455</v>
+        <v>70.9999939711293</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>37.86600895279948</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.89530779961259</v>
+        <v>7.834900248684574</v>
       </c>
       <c r="C21" t="n">
-        <v>105.5997418198184</v>
+        <v>100.8743407018139</v>
       </c>
       <c r="D21" t="n">
-        <v>9.869134749515737</v>
+        <v>8.814262779770146</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.970408700152354</v>
+        <v>6.6022533110598</v>
       </c>
       <c r="C2" t="n">
-        <v>9.6034560429423</v>
+        <v>8.252571201898688</v>
       </c>
       <c r="D2" t="n">
-        <v>29.71259426902972</v>
+        <v>29.26688081130166</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.10128424445344</v>
+        <v>17.88744317137688</v>
       </c>
       <c r="C3" t="n">
-        <v>36.11358930071892</v>
+        <v>25.0394751968149</v>
       </c>
       <c r="D3" t="n">
-        <v>85.20588325158067</v>
+        <v>87.0957475822558</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.35724265782137</v>
+        <v>33.00439432136928</v>
       </c>
       <c r="C4" t="n">
-        <v>65.75353423963438</v>
+        <v>58.08313942635404</v>
       </c>
       <c r="D4" t="n">
-        <v>124.487572393904</v>
+        <v>120.3396883434613</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.10563750809372</v>
+        <v>48.17926858591223</v>
       </c>
       <c r="C5" t="n">
-        <v>116.0671223345792</v>
+        <v>128.8543861823939</v>
       </c>
       <c r="D5" t="n">
-        <v>96.40762455703681</v>
+        <v>99.52467351802042</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.58124536530568</v>
+        <v>54.46049039768332</v>
       </c>
       <c r="C6" t="n">
-        <v>152.7550340422825</v>
+        <v>191.074610434444</v>
       </c>
       <c r="D6" t="n">
-        <v>62.02780170201773</v>
+        <v>66.25422556880025</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.8132566186774</v>
+        <v>45.15450390912779</v>
       </c>
       <c r="C7" t="n">
-        <v>144.6860496610779</v>
+        <v>201.8178755620168</v>
       </c>
       <c r="D7" t="n">
-        <v>45.6934833987593</v>
+        <v>48.14883440708056</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.6242369756475</v>
+        <v>28.87319998189869</v>
       </c>
       <c r="C8" t="n">
-        <v>114.574865824124</v>
+        <v>160.8053652171063</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.8640611529242</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>79.09843078346124</v>
+        <v>101.396866390019</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>58.36490101747288</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>37.84931924182727</v>
+        <v>38.73780091417063</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
         <v>35.58246379272139</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.06480566681026</v>
+        <v>7.991908635625726</v>
       </c>
       <c r="C21" t="n">
-        <v>113.9153800436949</v>
+        <v>107.8907665809473</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08910779186411</v>
+        <v>9.989885794532157</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.441246687563323</v>
+        <v>6.112361206640642</v>
       </c>
       <c r="C2" t="n">
-        <v>6.453027660014286</v>
+        <v>5.743224069843841</v>
       </c>
       <c r="D2" t="n">
-        <v>24.42391938625215</v>
+        <v>24.24916829489622</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.1019061392592</v>
+        <v>21.93715245139498</v>
       </c>
       <c r="C3" t="n">
-        <v>50.76617378660256</v>
+        <v>37.76292544385356</v>
       </c>
       <c r="D3" t="n">
-        <v>92.77024931280235</v>
+        <v>93.64891350810325</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.11328620108265</v>
+        <v>23.13881164139307</v>
       </c>
       <c r="C4" t="n">
-        <v>95.17160419739004</v>
+        <v>95.54172308189109</v>
       </c>
       <c r="D4" t="n">
-        <v>116.6257367782956</v>
+        <v>114.328447150358</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.72870314292517</v>
+        <v>30.67961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>91.2779928023472</v>
+        <v>114.1772580039041</v>
       </c>
       <c r="D5" t="n">
-        <v>63.88723185386119</v>
+        <v>66.34160111447822</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.41766904712818</v>
+        <v>28.01515248838698</v>
       </c>
       <c r="C6" t="n">
-        <v>95.27566945404023</v>
+        <v>132.9109676963417</v>
       </c>
       <c r="D6" t="n">
-        <v>30.06798693796707</v>
+        <v>31.67805317293184</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.64280806657018</v>
+        <v>19.10382857693868</v>
       </c>
       <c r="C7" t="n">
-        <v>80.54749039492954</v>
+        <v>113.0659196026967</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>58.24709129296325</v>
+        <v>74.68645660057609</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>44.48593372253571</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
         <v>28.43141351498762</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.91520984453628</v>
+        <v>3.781692156758713</v>
       </c>
       <c r="C2" t="n">
-        <v>2.670353755551324</v>
+        <v>2.543708301703486</v>
       </c>
       <c r="D2" t="n">
-        <v>17.30919377357552</v>
+        <v>18.1917849596934</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.91046533693107</v>
+        <v>22.0549621759046</v>
       </c>
       <c r="C3" t="n">
-        <v>38.2734342500619</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D3" t="n">
-        <v>91.41543748094176</v>
+        <v>92.90278525287567</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.24688600431823</v>
+        <v>31.01340997715674</v>
       </c>
       <c r="C4" t="n">
-        <v>113.2436159371653</v>
+        <v>97.494419265638</v>
       </c>
       <c r="D4" t="n">
-        <v>134.4424941149667</v>
+        <v>130.5371017474729</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.26299487821369</v>
+        <v>33.74757733348411</v>
       </c>
       <c r="C5" t="n">
-        <v>132.5113963807133</v>
+        <v>145.3232039211341</v>
       </c>
       <c r="D5" t="n">
-        <v>83.17857424231102</v>
+        <v>85.38750657686634</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.09315252537899</v>
+        <v>33.32837106377072</v>
       </c>
       <c r="C6" t="n">
-        <v>120.3927027194906</v>
+        <v>157.987749305918</v>
       </c>
       <c r="D6" t="n">
-        <v>37.75605320992383</v>
+        <v>38.88309957439917</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>103.6038352291659</v>
+        <v>145.3448023706275</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.42239785920016</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>76.52232480751763</v>
+        <v>98.30239762623312</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>44.04218376021615</v>
+        <v>49.69999577979051</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.679590395517045</v>
+        <v>3.506802799569606</v>
       </c>
       <c r="C2" t="n">
-        <v>4.654465865834128</v>
+        <v>7.486807992586176</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5740446695439</v>
+        <v>23.98605991015807</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.54521413322225</v>
+        <v>17.43583922742335</v>
       </c>
       <c r="C3" t="n">
-        <v>23.29687302177681</v>
+        <v>19.92456965768902</v>
       </c>
       <c r="D3" t="n">
-        <v>85.29914928348413</v>
+        <v>86.39379797371932</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.51338160052563</v>
+        <v>36.41204060280995</v>
       </c>
       <c r="C4" t="n">
-        <v>104.0289319851048</v>
+        <v>86.97793785774617</v>
       </c>
       <c r="D4" t="n">
-        <v>145.903416814344</v>
+        <v>144.6781956794439</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.50338419703392</v>
+        <v>39.56443248114646</v>
       </c>
       <c r="C5" t="n">
-        <v>171.9531103988289</v>
+        <v>161.7183905820559</v>
       </c>
       <c r="D5" t="n">
-        <v>109.26851948267</v>
+        <v>108.2131407006047</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.7686360036298</v>
+        <v>38.80259626265094</v>
       </c>
       <c r="C6" t="n">
-        <v>162.9387029784347</v>
+        <v>193.4897097868912</v>
       </c>
       <c r="D6" t="n">
-        <v>52.36740429222912</v>
+        <v>52.93092747446678</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.5478405811655</v>
+        <v>26.52976821186155</v>
       </c>
       <c r="C7" t="n">
-        <v>137.8589761257456</v>
+        <v>183.0733666448324</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>12.51728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>105.1451791248334</v>
+        <v>141.0280577150543</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>66.45155685735384</v>
+        <v>80.76249314215958</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.172607669498191</v>
+        <v>2.113702807243383</v>
       </c>
       <c r="C2" t="n">
-        <v>2.146100481483527</v>
+        <v>3.575525138866883</v>
       </c>
       <c r="D2" t="n">
-        <v>10.06095047312131</v>
+        <v>16.75646981608456</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.00034415736527</v>
+        <v>16.8516993433965</v>
       </c>
       <c r="C3" t="n">
-        <v>22.54092728950677</v>
+        <v>25.09347132054847</v>
       </c>
       <c r="D3" t="n">
-        <v>81.85812358009906</v>
+        <v>87.94495934642927</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.39324852770901</v>
+        <v>40.02389040673396</v>
       </c>
       <c r="C4" t="n">
-        <v>97.23916486253384</v>
+        <v>82.37059588171589</v>
       </c>
       <c r="D4" t="n">
-        <v>156.2922710206837</v>
+        <v>154.6714055609722</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.0005494460103</v>
+        <v>41.33157834879072</v>
       </c>
       <c r="C5" t="n">
-        <v>204.2035224833366</v>
+        <v>188.1274038262951</v>
       </c>
       <c r="D5" t="n">
-        <v>118.055161435679</v>
+        <v>114.3245201595411</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.61013265488955</v>
+        <v>31.87931145230244</v>
       </c>
       <c r="C6" t="n">
-        <v>196.9916038479395</v>
+        <v>230.7627431263256</v>
       </c>
       <c r="D6" t="n">
-        <v>51.15985461600555</v>
+        <v>51.72337779824321</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.743445054022093</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>142.1109254328385</v>
+        <v>188.6428213710246</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>81.94648087348126</v>
+        <v>102.3079282595601</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.065016332658542</v>
+        <v>2.667408512438584</v>
       </c>
       <c r="C2" t="n">
-        <v>4.142975311921539</v>
+        <v>7.570256547447155</v>
       </c>
       <c r="D2" t="n">
-        <v>14.32468075266521</v>
+        <v>18.16920476249572</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.85107744859075</v>
+        <v>12.22275891787279</v>
       </c>
       <c r="C3" t="n">
-        <v>15.19745446174063</v>
+        <v>19.43369580556561</v>
       </c>
       <c r="D3" t="n">
-        <v>72.06519023023712</v>
+        <v>82.30972752405259</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.60272064161208</v>
+        <v>36.71834588653496</v>
       </c>
       <c r="C4" t="n">
-        <v>77.5973385436679</v>
+        <v>73.38564089244908</v>
       </c>
       <c r="D4" t="n">
-        <v>160.7592230750067</v>
+        <v>161.3335454819911</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.59713325502288</v>
+        <v>49.2837347531899</v>
       </c>
       <c r="C5" t="n">
-        <v>194.1406085148068</v>
+        <v>172.8857707178633</v>
       </c>
       <c r="D5" t="n">
-        <v>143.6296891313084</v>
+        <v>137.1992416684918</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.51203999992289</v>
+        <v>40.89568236810514</v>
       </c>
       <c r="C6" t="n">
-        <v>255.3565048654124</v>
+        <v>263.0445711373692</v>
       </c>
       <c r="D6" t="n">
-        <v>69.63536466222628</v>
+        <v>69.2730997593592</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.74450891718435</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>205.4709587695192</v>
+        <v>252.9011538570911</v>
       </c>
       <c r="D7" t="n">
-        <v>40.18391528252619</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>125.5900750657732</v>
+        <v>160.8888137719673</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>57.35468262980289</v>
+        <v>66.11874438561416</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.289435646303562</v>
+        <v>1.870229376590174</v>
       </c>
       <c r="C2" t="n">
-        <v>3.160245859970483</v>
+        <v>4.18911745402114</v>
       </c>
       <c r="D2" t="n">
-        <v>11.21548577331556</v>
+        <v>12.852059196295</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.96750451476862</v>
+        <v>11.02011798017045</v>
       </c>
       <c r="C3" t="n">
-        <v>15.77177686872501</v>
+        <v>24.14117604742907</v>
       </c>
       <c r="D3" t="n">
-        <v>68.08911202803753</v>
+        <v>79.6442825070225</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.80393786325368</v>
+        <v>32.51941095547134</v>
       </c>
       <c r="C4" t="n">
-        <v>62.48627787990099</v>
+        <v>64.7452793473729</v>
       </c>
       <c r="D4" t="n">
-        <v>160.9889520378005</v>
+        <v>164.5497509611036</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.18680377237672</v>
+        <v>53.30890034060182</v>
       </c>
       <c r="C5" t="n">
-        <v>181.1569951261427</v>
+        <v>164.6390900021901</v>
       </c>
       <c r="D5" t="n">
-        <v>161.0802545742954</v>
+        <v>152.6126806251667</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.07935130425731</v>
+        <v>47.61770889908305</v>
       </c>
       <c r="C6" t="n">
-        <v>285.4647434592536</v>
+        <v>280.2722798514922</v>
       </c>
       <c r="D6" t="n">
-        <v>84.48822567977626</v>
+        <v>83.9247024975386</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>16.10949807898591</v>
       </c>
       <c r="C7" t="n">
-        <v>262.1835784007447</v>
+        <v>302.6669267330661</v>
       </c>
       <c r="D7" t="n">
-        <v>45.75337000871835</v>
+        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>163.4757189726576</v>
+        <v>205.533790622591</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>67.11718180083317</v>
+        <v>75.10468112258522</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.764020698082271</v>
+        <v>3.241730919422968</v>
       </c>
       <c r="C2" t="n">
-        <v>7.820602212030092</v>
+        <v>12.23159464721101</v>
       </c>
       <c r="D2" t="n">
-        <v>15.5116137270996</v>
+        <v>13.07098893434203</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.910743074371553</v>
+        <v>8.791550691530187</v>
       </c>
       <c r="C3" t="n">
-        <v>14.01444847812322</v>
+        <v>20.34672117051515</v>
       </c>
       <c r="D3" t="n">
-        <v>62.28698309593889</v>
+        <v>72.69841749947631</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.11176467403067</v>
+        <v>27.09525488950772</v>
       </c>
       <c r="C4" t="n">
-        <v>51.90598287123311</v>
+        <v>62.56285420083224</v>
       </c>
       <c r="D4" t="n">
-        <v>158.3981198462931</v>
+        <v>165.6601076146068</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.29693944170161</v>
+        <v>51.56629816556373</v>
       </c>
       <c r="C5" t="n">
-        <v>152.1954378508618</v>
+        <v>145.0286796098601</v>
       </c>
       <c r="D5" t="n">
-        <v>174.5792855076891</v>
+        <v>169.9896149903352</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.22276858453534</v>
+        <v>56.714583126634</v>
       </c>
       <c r="C6" t="n">
-        <v>287.5578295647078</v>
+        <v>273.9527698792555</v>
       </c>
       <c r="D6" t="n">
-        <v>107.5121728397725</v>
+        <v>103.6077622199829</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.27888276793088</v>
+        <v>29.46421209985527</v>
       </c>
       <c r="C7" t="n">
-        <v>326.7413439366064</v>
+        <v>348.0609770820301</v>
       </c>
       <c r="D7" t="n">
-        <v>55.45500082208532</v>
+        <v>52.99964981376406</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>234.5738877142116</v>
+        <v>279.5526587842793</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>117.7046775052628</v>
+        <v>139.7812381306608</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>48.9695754878309</v>
+        <v>50.96252332745193</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.840016181936775</v>
+        <v>5.880668748438394</v>
       </c>
       <c r="C2" t="n">
-        <v>5.21406205725481</v>
+        <v>8.749335540247575</v>
       </c>
       <c r="D2" t="n">
-        <v>8.206429059799088</v>
+        <v>8.411614329986671</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.690970457340507</v>
+        <v>2.343431770037137</v>
       </c>
       <c r="C2" t="n">
-        <v>4.442408361716817</v>
+        <v>7.046003273379358</v>
       </c>
       <c r="D2" t="n">
-        <v>11.41674405268616</v>
+        <v>9.724211010564657</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.62665813494573</v>
+        <v>12.15894531709675</v>
       </c>
       <c r="C3" t="n">
-        <v>21.04376204053038</v>
+        <v>31.27848185730338</v>
       </c>
       <c r="D3" t="n">
-        <v>68.84996649882882</v>
+        <v>77.72987448374121</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.38950146334128</v>
+        <v>38.5817030291954</v>
       </c>
       <c r="C4" t="n">
-        <v>77.98022014832415</v>
+        <v>89.01997308257953</v>
       </c>
       <c r="D4" t="n">
-        <v>162.3290376540974</v>
+        <v>169.1060420565131</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.00559705325178</v>
+        <v>32.88854809226815</v>
       </c>
       <c r="C5" t="n">
-        <v>236.7975462643307</v>
+        <v>225.875603054585</v>
       </c>
       <c r="D5" t="n">
-        <v>159.4849145548944</v>
+        <v>153.3244477107456</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.04532462531138</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="C6" t="n">
-        <v>271.5779221826825</v>
+        <v>280.2722798514922</v>
       </c>
       <c r="D6" t="n">
-        <v>84.44797402390215</v>
+        <v>81.10708658635025</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>164.9277238272387</v>
+        <v>196.607740495579</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>32.39865598784899</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>86.70304850055705</v>
+        <v>102.9755166984479</v>
       </c>
       <c r="D8" t="n">
-        <v>25.2849121228766</v>
+        <v>24.45042657426681</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.38593432542277</v>
+        <v>38.82812170296133</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.33129094468768</v>
+        <v>6.600289815651307</v>
       </c>
       <c r="C2" t="n">
-        <v>4.569053815564656</v>
+        <v>7.3719435111893</v>
       </c>
       <c r="D2" t="n">
-        <v>10.63723637551419</v>
+        <v>20.25541863402019</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.28380720198534</v>
+        <v>12.49273953654066</v>
       </c>
       <c r="C3" t="n">
-        <v>13.34686003923539</v>
+        <v>22.04514469886213</v>
       </c>
       <c r="D3" t="n">
-        <v>10.02855279888117</v>
+        <v>10.20035864712436</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4574,7 +4574,7 @@
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39886793229715</v>
+        <v>13.39804628004896</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14701446908508</v>
+        <v>70.14271287790335</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576337403799665</v>
+        <v>1.576240738829289</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.600469742100554</v>
+        <v>4.424736903040374</v>
       </c>
       <c r="C2" t="n">
-        <v>4.587707021945345</v>
+        <v>5.917975161199774</v>
       </c>
       <c r="D2" t="n">
-        <v>9.568113125589415</v>
+        <v>22.71175139004571</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.20512851692535</v>
+        <v>18.67775007329557</v>
       </c>
       <c r="C3" t="n">
-        <v>16.19883712007237</v>
+        <v>26.23720739599601</v>
       </c>
       <c r="D3" t="n">
-        <v>16.53754007803752</v>
+        <v>24.74985962406209</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.03524510636165</v>
+        <v>14.54950097693773</v>
       </c>
       <c r="C4" t="n">
-        <v>21.21164089795658</v>
+        <v>34.14027641518283</v>
       </c>
       <c r="D4" t="n">
-        <v>20.3310132072472</v>
+        <v>20.42035224833366</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44470157869987</v>
+        <v>15.43926885931322</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16517722853612</v>
+        <v>86.1348683730106</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251516121831552</v>
+        <v>3.250372391434362</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.70944373727195</v>
+        <v>5.330890034060181</v>
       </c>
       <c r="C2" t="n">
-        <v>4.57690779719863</v>
+        <v>7.03913103944963</v>
       </c>
       <c r="D2" t="n">
-        <v>25.2682224119044</v>
+        <v>22.1766988912312</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.52772260099505</v>
+        <v>16.78788574262046</v>
       </c>
       <c r="C3" t="n">
-        <v>17.22967220953152</v>
+        <v>24.54369260617026</v>
       </c>
       <c r="D3" t="n">
-        <v>20.35162990903638</v>
+        <v>37.17387682130548</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.3767954964483</v>
+        <v>26.84000048640355</v>
       </c>
       <c r="C4" t="n">
-        <v>32.80019079888594</v>
+        <v>52.07189823325082</v>
       </c>
       <c r="D4" t="n">
-        <v>23.86628669023996</v>
+        <v>28.23113698332128</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.94648690235194</v>
+        <v>12.7136327699962</v>
       </c>
       <c r="C5" t="n">
-        <v>24.98547907308133</v>
+        <v>38.28816046562561</v>
       </c>
       <c r="D5" t="n">
-        <v>30.13965452037709</v>
+        <v>30.01693605734623</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
         <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74488899329562</v>
+        <v>16.72955117224544</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1438228591033</v>
+        <v>102.0502621506972</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023466697988686</v>
+        <v>4.18238779306136</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.914629007459533</v>
+        <v>5.465389469541994</v>
       </c>
       <c r="C2" t="n">
-        <v>8.059166904162065</v>
+        <v>13.72385115766616</v>
       </c>
       <c r="D2" t="n">
-        <v>35.7670323611198</v>
+        <v>32.96806965631214</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.31664684458199</v>
+        <v>17.5291052593268</v>
       </c>
       <c r="C3" t="n">
-        <v>17.5438314748905</v>
+        <v>26.13412388705009</v>
       </c>
       <c r="D3" t="n">
-        <v>35.02875808752619</v>
+        <v>45.75926049494383</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.42257778564941</v>
+        <v>29.67332436085984</v>
       </c>
       <c r="C4" t="n">
-        <v>38.67104207028186</v>
+        <v>57.29185077673112</v>
       </c>
       <c r="D4" t="n">
-        <v>28.20561154301086</v>
+        <v>39.84521232456105</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.02827506144069</v>
+        <v>26.48264432205772</v>
       </c>
       <c r="C5" t="n">
-        <v>44.57134577280519</v>
+        <v>69.53228115328035</v>
       </c>
       <c r="D5" t="n">
-        <v>32.07860623626453</v>
+        <v>32.98672286269284</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.38492721552276</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C6" t="n">
-        <v>26.56609287691869</v>
+        <v>37.19253002768617</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95731148929444</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
         <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.60155896745857</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07926391124617</v>
+        <v>18.05050705411068</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9456740876536</v>
+        <v>117.7580698291982</v>
       </c>
       <c r="D21" t="n">
-        <v>6.887338632855685</v>
+        <v>6.016835684703558</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.388232311533995</v>
+        <v>6.267477343911637</v>
       </c>
       <c r="C2" t="n">
-        <v>8.370380926408306</v>
+        <v>7.65174160689964</v>
       </c>
       <c r="D2" t="n">
-        <v>33.96650707153115</v>
+        <v>28.53744226704629</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.85875150377547</v>
+        <v>16.10557108816893</v>
       </c>
       <c r="C3" t="n">
-        <v>24.06263623108932</v>
+        <v>38.87230034965246</v>
       </c>
       <c r="D3" t="n">
-        <v>51.1883252994287</v>
+        <v>57.04445035526092</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.1305567491316</v>
+        <v>23.03670988015141</v>
       </c>
       <c r="C4" t="n">
-        <v>34.90603962449534</v>
+        <v>51.15298238207581</v>
       </c>
       <c r="D4" t="n">
-        <v>33.6425303291297</v>
+        <v>46.30314872309656</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.469439633546</v>
+        <v>21.64753687864217</v>
       </c>
       <c r="C5" t="n">
-        <v>43.76140391680158</v>
+        <v>66.1207078810227</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>31.73499453977815</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.83398682699105</v>
+        <v>12.92078153559227</v>
       </c>
       <c r="C6" t="n">
-        <v>34.01264921363075</v>
+        <v>50.59633143376788</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47050349670826</v>
+        <v>31.11452999069417</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>19.40326162673396</v>
+        <v>23.83487076370406</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.069195665609535</v>
+        <v>7.051358360375794</v>
       </c>
       <c r="C21" t="n">
-        <v>67.15735882329058</v>
+        <v>66.10648462852306</v>
       </c>
       <c r="D21" t="n">
-        <v>5.301896749207152</v>
+        <v>4.407098975234871</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.641703145678919</v>
+        <v>5.325981295538947</v>
       </c>
       <c r="C2" t="n">
-        <v>7.973754853892594</v>
+        <v>5.832563110930301</v>
       </c>
       <c r="D2" t="n">
-        <v>32.7471764228566</v>
+        <v>24.59376173908684</v>
       </c>
     </row>
     <row r="3">
@@ -6084,10 +6084,10 @@
         <v>19.62022786937251</v>
       </c>
       <c r="C3" t="n">
-        <v>29.74204670015712</v>
+        <v>33.15361997241479</v>
       </c>
       <c r="D3" t="n">
-        <v>68.21673922958962</v>
+        <v>67.23008278682157</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.81447504609313</v>
+        <v>28.35876418487337</v>
       </c>
       <c r="C4" t="n">
-        <v>51.16574510223102</v>
+        <v>79.79252641036376</v>
       </c>
       <c r="D4" t="n">
-        <v>53.61618737203106</v>
+        <v>65.45999167606458</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.29887757491431</v>
+        <v>29.05973204570559</v>
       </c>
       <c r="C5" t="n">
-        <v>56.32777453116076</v>
+        <v>82.66315669758144</v>
       </c>
       <c r="D5" t="n">
-        <v>34.92567457858028</v>
+        <v>41.45429681182157</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.05161602216436</v>
+        <v>22.37992066601029</v>
       </c>
       <c r="C6" t="n">
-        <v>55.6680400739069</v>
+        <v>82.71715282131501</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>34.65667570761666</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.54004335279375</v>
+        <v>11.13890945238431</v>
       </c>
       <c r="C7" t="n">
-        <v>37.42913122440964</v>
+        <v>52.52055693409162</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>23.19869825135213</v>
+        <v>26.45319189093031</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295725720125843</v>
+        <v>7.269335870155833</v>
       </c>
       <c r="C21" t="n">
-        <v>77.51708577633708</v>
+        <v>75.41935965286677</v>
       </c>
       <c r="D21" t="n">
-        <v>6.383760005110113</v>
+        <v>5.452001902616875</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.009858534771474</v>
+        <v>4.911683764346792</v>
       </c>
       <c r="C2" t="n">
-        <v>4.990223580686537</v>
+        <v>5.465389469541994</v>
       </c>
       <c r="D2" t="n">
-        <v>28.02202472231671</v>
+        <v>25.97311726355361</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.63709750679395</v>
+        <v>18.91827826083604</v>
       </c>
       <c r="C3" t="n">
-        <v>30.55689729468197</v>
+        <v>26.89497835784137</v>
       </c>
       <c r="D3" t="n">
-        <v>78.58399498643594</v>
+        <v>71.95228924424873</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.60424216866407</v>
+        <v>33.89778473223387</v>
       </c>
       <c r="C4" t="n">
-        <v>65.16644911249479</v>
+        <v>81.69417171348984</v>
       </c>
       <c r="D4" t="n">
-        <v>75.22347259479911</v>
+        <v>82.77900292668257</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.92567457858028</v>
+        <v>36.12831551628263</v>
       </c>
       <c r="C5" t="n">
-        <v>78.56436003235102</v>
+        <v>118.9878217547134</v>
       </c>
       <c r="D5" t="n">
-        <v>46.95208395560371</v>
+        <v>55.59146375297565</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.83276839957533</v>
+        <v>31.5975498611836</v>
       </c>
       <c r="C6" t="n">
-        <v>74.18380177600174</v>
+        <v>109.1624907306114</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>39.56737772425921</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C7" t="n">
-        <v>61.86286808770426</v>
+        <v>87.91354341989337</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>38.21943812632832</v>
+        <v>49.73533869714341</v>
       </c>
       <c r="D8" t="n">
-        <v>34.79804737702819</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.06874770149305</v>
+        <v>28.84374755077128</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.509763099451258</v>
+        <v>7.47333480342644</v>
       </c>
       <c r="C21" t="n">
-        <v>87.30099603112087</v>
+        <v>84.07501653854744</v>
       </c>
       <c r="D21" t="n">
-        <v>7.509763099451258</v>
+        <v>6.539167952998135</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_13_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497619106077</v>
+        <v>10.84497625379933</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890714500606</v>
+        <v>37.7890716686717</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.570436473896402</v>
+        <v>0.7137305809874311</v>
       </c>
       <c r="C2" t="n">
-        <v>4.240168334641973</v>
+        <v>2.863758053287946</v>
       </c>
       <c r="D2" t="n">
-        <v>30.65801730821939</v>
+        <v>15.14640358111979</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.66654993792135</v>
+        <v>7.117670855789375</v>
       </c>
       <c r="C3" t="n">
-        <v>23.71902453460294</v>
+        <v>29.40334374219197</v>
       </c>
       <c r="D3" t="n">
-        <v>75.33931882390023</v>
+        <v>69.28193548869741</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.89327690434013</v>
+        <v>13.14560175986479</v>
       </c>
       <c r="C4" t="n">
-        <v>73.99825145989908</v>
+        <v>93.1806198531775</v>
       </c>
       <c r="D4" t="n">
-        <v>98.27294519510572</v>
+        <v>80.13711985455438</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.56505437595222</v>
+        <v>11.92823460659875</v>
       </c>
       <c r="C5" t="n">
-        <v>134.0085616296896</v>
+        <v>124.4610652058894</v>
       </c>
       <c r="D5" t="n">
-        <v>70.26859193146547</v>
+        <v>49.40645321622075</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.92964262712628</v>
+        <v>8.774860980557992</v>
       </c>
       <c r="C6" t="n">
-        <v>149.2933916371082</v>
+        <v>94.43038468068373</v>
       </c>
       <c r="D6" t="n">
-        <v>47.41645061971246</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.32636651063322</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>122.048911096555</v>
+        <v>51.62225778470578</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>83.19820919639595</v>
+        <v>30.12492830481337</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>45.26249615659493</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.662053604831931</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.90239995858715</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.662053604831931</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.478152189697202</v>
+        <v>0.4378594760940774</v>
       </c>
       <c r="C2" t="n">
-        <v>8.12592574805085</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="D2" t="n">
-        <v>35.85833489761475</v>
+        <v>20.47238487665874</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.94143929511046</v>
+        <v>4.614214209960009</v>
       </c>
       <c r="C3" t="n">
-        <v>19.97856578142259</v>
+        <v>18.66302385773187</v>
       </c>
       <c r="D3" t="n">
-        <v>80.37077580816513</v>
+        <v>65.38439710283757</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.78292025083699</v>
+        <v>13.63058512576272</v>
       </c>
       <c r="C4" t="n">
-        <v>66.05983952335937</v>
+        <v>82.97044372901068</v>
       </c>
       <c r="D4" t="n">
-        <v>109.3254608495163</v>
+        <v>95.93736740670256</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.24660826687776</v>
+        <v>15.85522542358599</v>
       </c>
       <c r="C5" t="n">
-        <v>134.9412219487241</v>
+        <v>150.2319424423682</v>
       </c>
       <c r="D5" t="n">
-        <v>86.34471058850698</v>
+        <v>65.97344572538567</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.66425195181016</v>
+        <v>12.39751000922872</v>
       </c>
       <c r="C6" t="n">
-        <v>176.8657759108799</v>
+        <v>149.0518817018635</v>
       </c>
       <c r="D6" t="n">
-        <v>56.07055663264809</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.77037851486003</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>165.1073836571158</v>
+        <v>94.74061695522569</v>
       </c>
       <c r="D7" t="n">
-        <v>43.05847256056086</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.61317570899353</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>118.0797051282851</v>
+        <v>49.48499303256047</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>70.9999939711293</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.834900248684574</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8743407018139</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.814262779770146</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.6022533110598</v>
+        <v>0.2316924582022472</v>
       </c>
       <c r="C2" t="n">
-        <v>8.252571201898688</v>
+        <v>3.674681656995811</v>
       </c>
       <c r="D2" t="n">
-        <v>29.26688081130166</v>
+        <v>13.94670788653019</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.88744317137688</v>
+        <v>3.77972866135022</v>
       </c>
       <c r="C3" t="n">
-        <v>25.0394751968149</v>
+        <v>27.57238427377167</v>
       </c>
       <c r="D3" t="n">
-        <v>87.0957475822558</v>
+        <v>68.1431081517711</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.00439432136928</v>
+        <v>14.68989089864502</v>
       </c>
       <c r="C4" t="n">
-        <v>58.08313942635404</v>
+        <v>75.97647308395641</v>
       </c>
       <c r="D4" t="n">
-        <v>120.3396883434613</v>
+        <v>105.4455939223329</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.17926858591223</v>
+        <v>16.07611865704152</v>
       </c>
       <c r="C5" t="n">
-        <v>128.8543861823939</v>
+        <v>171.2413433132499</v>
       </c>
       <c r="D5" t="n">
-        <v>99.52467351802042</v>
+        <v>74.22012644105888</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.46049039768332</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>191.074610434444</v>
+        <v>188.9010210172416</v>
       </c>
       <c r="D6" t="n">
-        <v>66.25422556880025</v>
+        <v>38.76234460677682</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.15450390912779</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>201.8178755620168</v>
+        <v>90.00957476846031</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.87319998189869</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>160.8053652171063</v>
+        <v>43.30979997284804</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.08749871886498</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>101.396866390019</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>58.36490101747288</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.991908635625726</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8907665809473</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.989885794532157</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.112361206640642</v>
+        <v>0.3485204350076176</v>
       </c>
       <c r="C2" t="n">
-        <v>5.743224069843841</v>
+        <v>7.218790869326797</v>
       </c>
       <c r="D2" t="n">
-        <v>24.24916829489622</v>
+        <v>16.05942894606932</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.93715245139498</v>
+        <v>2.22856728864026</v>
       </c>
       <c r="C3" t="n">
-        <v>37.76292544385356</v>
+        <v>20.14055415262332</v>
       </c>
       <c r="D3" t="n">
-        <v>93.64891350810325</v>
+        <v>64.24066102739003</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.13881164139307</v>
+        <v>11.19290557611789</v>
       </c>
       <c r="C4" t="n">
-        <v>95.54172308189109</v>
+        <v>72.84960664593032</v>
       </c>
       <c r="D4" t="n">
-        <v>114.328447150358</v>
+        <v>114.6219897139279</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.67961575771283</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="C5" t="n">
-        <v>114.1772580039041</v>
+        <v>156.7605646756095</v>
       </c>
       <c r="D5" t="n">
-        <v>66.34160111447822</v>
+        <v>92.92242020696061</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.01515248838698</v>
+        <v>15.41638419978766</v>
       </c>
       <c r="C6" t="n">
-        <v>132.9109676963417</v>
+        <v>233.9023722845069</v>
       </c>
       <c r="D6" t="n">
-        <v>31.67805317293184</v>
+        <v>51.36111289537615</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>113.0659196026967</v>
+        <v>175.9468600597048</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>74.68645660057609</v>
+        <v>77.10646469154449</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>44.48593372253571</v>
+        <v>38.38437174064178</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.781692156758713</v>
+        <v>0.2434734306532089</v>
       </c>
       <c r="C2" t="n">
-        <v>2.543708301703486</v>
+        <v>3.917173339944773</v>
       </c>
       <c r="D2" t="n">
-        <v>18.1917849596934</v>
+        <v>12.36511233498858</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.0549621759046</v>
+        <v>1.791689560250429</v>
       </c>
       <c r="C3" t="n">
-        <v>30.69925071179776</v>
+        <v>24.77931205518949</v>
       </c>
       <c r="D3" t="n">
-        <v>92.90278525287567</v>
+        <v>62.72386082432871</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.01340997715674</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C4" t="n">
-        <v>97.494419265638</v>
+        <v>63.99227885821559</v>
       </c>
       <c r="D4" t="n">
-        <v>130.5371017474729</v>
+        <v>121.3862313961884</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.74757733348411</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C5" t="n">
-        <v>145.3232039211341</v>
+        <v>152.6372243177729</v>
       </c>
       <c r="D5" t="n">
-        <v>85.38750657686634</v>
+        <v>106.8877812998715</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.32837106377072</v>
+        <v>18.6365166697172</v>
       </c>
       <c r="C6" t="n">
-        <v>157.987749305918</v>
+        <v>251.7741074926158</v>
       </c>
       <c r="D6" t="n">
-        <v>38.88309957439917</v>
+        <v>62.87308647537424</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>145.3448023706275</v>
+        <v>238.5283674669178</v>
       </c>
       <c r="D7" t="n">
-        <v>30.42239785920016</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>98.30239762623312</v>
+        <v>119.4983305609218</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>49.69999577979051</v>
+        <v>50.36562072326985</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.506802799569606</v>
+        <v>0.2316924582022472</v>
       </c>
       <c r="C2" t="n">
-        <v>7.486807992586176</v>
+        <v>14.06746285415255</v>
       </c>
       <c r="D2" t="n">
-        <v>23.98605991015807</v>
+        <v>21.27643624643687</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.43583922742335</v>
+        <v>1.305724446648258</v>
       </c>
       <c r="C3" t="n">
-        <v>19.92456965768902</v>
+        <v>19.72822011683965</v>
       </c>
       <c r="D3" t="n">
-        <v>86.39379797371932</v>
+        <v>58.38453597155781</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.41204060280995</v>
+        <v>6.202681995431348</v>
       </c>
       <c r="C4" t="n">
-        <v>86.97793785774617</v>
+        <v>62.86915948455724</v>
       </c>
       <c r="D4" t="n">
-        <v>144.6781956794439</v>
+        <v>124.5003351140593</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.56443248114646</v>
+        <v>17.18058482431918</v>
       </c>
       <c r="C5" t="n">
-        <v>161.7183905820559</v>
+        <v>137.2974164389165</v>
       </c>
       <c r="D5" t="n">
-        <v>108.2131407006047</v>
+        <v>123.0620747273377</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.80259626265094</v>
+        <v>22.09815907489146</v>
       </c>
       <c r="C6" t="n">
-        <v>193.4897097868912</v>
+        <v>248.7552333020569</v>
       </c>
       <c r="D6" t="n">
-        <v>52.93092747446678</v>
+        <v>78.20896736341366</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.52976821186155</v>
+        <v>13.59426046070558</v>
       </c>
       <c r="C7" t="n">
-        <v>183.0733666448324</v>
+        <v>298.0556577662189</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>46.65166915810418</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>141.0280577150543</v>
+        <v>204.0317166350934</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>41.47393176590651</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>80.76249314215958</v>
+        <v>90.0812423508703</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>42.82187136383736</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.113702807243383</v>
+        <v>0.1570796326794897</v>
       </c>
       <c r="C2" t="n">
-        <v>3.575525138866883</v>
+        <v>7.427903130331368</v>
       </c>
       <c r="D2" t="n">
-        <v>16.75646981608456</v>
+        <v>15.48903352990193</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8516993433965</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C3" t="n">
-        <v>25.09347132054847</v>
+        <v>35.03857556456867</v>
       </c>
       <c r="D3" t="n">
-        <v>87.94495934642927</v>
+        <v>66.00289815651307</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.02389040673396</v>
+        <v>11.20566829627309</v>
       </c>
       <c r="C4" t="n">
-        <v>82.37059588171589</v>
+        <v>87.41187034302325</v>
       </c>
       <c r="D4" t="n">
-        <v>154.6714055609722</v>
+        <v>127.665489712551</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.33157834879072</v>
+        <v>13.54811831860599</v>
       </c>
       <c r="C5" t="n">
-        <v>188.1274038262951</v>
+        <v>207.860532681656</v>
       </c>
       <c r="D5" t="n">
-        <v>114.3245201595411</v>
+        <v>113.8581900000239</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.87931145230244</v>
+        <v>8.412596077690921</v>
       </c>
       <c r="C6" t="n">
-        <v>230.7627431263256</v>
+        <v>254.7929816831747</v>
       </c>
       <c r="D6" t="n">
-        <v>51.72337779824321</v>
+        <v>65.20768251607315</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.26435217434965</v>
+        <v>3.952516257297658</v>
       </c>
       <c r="C7" t="n">
-        <v>188.6428213710246</v>
+        <v>143.4883174618968</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>102.3079282595601</v>
+        <v>66.34160111447821</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>34.75877746885832</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.667408512438584</v>
+        <v>0.07068583470577035</v>
       </c>
       <c r="C2" t="n">
-        <v>7.570256547447155</v>
+        <v>3.510729790386593</v>
       </c>
       <c r="D2" t="n">
-        <v>18.16920476249572</v>
+        <v>10.98182981970482</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.22275891787279</v>
+        <v>1.227184630308513</v>
       </c>
       <c r="C3" t="n">
-        <v>19.43369580556561</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D3" t="n">
-        <v>82.30972752405259</v>
+        <v>62.91530162665685</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.71834588653496</v>
+        <v>7.096072406295946</v>
       </c>
       <c r="C4" t="n">
-        <v>73.38564089244908</v>
+        <v>84.66788550965342</v>
       </c>
       <c r="D4" t="n">
-        <v>161.3335454819911</v>
+        <v>125.8787088908218</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.2837347531899</v>
+        <v>12.17367153266045</v>
       </c>
       <c r="C5" t="n">
-        <v>172.8857707178633</v>
+        <v>166.3080610994097</v>
       </c>
       <c r="D5" t="n">
-        <v>137.1992416684918</v>
+        <v>119.65050145508</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.89568236810514</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>263.0445711373692</v>
+        <v>241.711193524086</v>
       </c>
       <c r="D6" t="n">
-        <v>69.2730997593592</v>
+        <v>69.19259644761097</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>3.173990327829938</v>
       </c>
       <c r="C7" t="n">
-        <v>252.9011538570911</v>
+        <v>175.5875403999505</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>160.8888137719673</v>
+        <v>75.60439070404686</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>66.11874438561416</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>18.07888397370501</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.870229376590174</v>
+        <v>0.150207398749762</v>
       </c>
       <c r="C2" t="n">
-        <v>4.18911745402114</v>
+        <v>8.285950623843078</v>
       </c>
       <c r="D2" t="n">
-        <v>12.852059196295</v>
+        <v>10.234719816773</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.02011798017045</v>
+        <v>0.6872233929727672</v>
       </c>
       <c r="C3" t="n">
-        <v>24.14117604742907</v>
+        <v>21.12721059539136</v>
       </c>
       <c r="D3" t="n">
-        <v>79.6442825070225</v>
+        <v>57.26534358871645</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.51941095547134</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C4" t="n">
-        <v>64.7452793473729</v>
+        <v>81.80903619488672</v>
       </c>
       <c r="D4" t="n">
-        <v>164.5497509611036</v>
+        <v>128.9162362877614</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.30890034060182</v>
+        <v>11.73188506574938</v>
       </c>
       <c r="C5" t="n">
-        <v>164.6390900021901</v>
+        <v>162.601963515878</v>
       </c>
       <c r="D5" t="n">
-        <v>152.6126806251667</v>
+        <v>137.1501542832794</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.61770889908305</v>
+        <v>12.15600007398401</v>
       </c>
       <c r="C6" t="n">
-        <v>280.2722798514922</v>
+        <v>254.5917234038041</v>
       </c>
       <c r="D6" t="n">
-        <v>83.9247024975386</v>
+        <v>88.9561594818035</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.10949807898591</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>302.6669267330661</v>
+        <v>267.3937134671825</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>45.21439051908685</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>205.533790622591</v>
+        <v>154.129480828228</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>75.10468112258522</v>
+        <v>61.68124476241858</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>22.74218556887735</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.241730919422968</v>
+        <v>0.08639379797371931</v>
       </c>
       <c r="C2" t="n">
-        <v>12.23159464721101</v>
+        <v>8.358599953957343</v>
       </c>
       <c r="D2" t="n">
-        <v>13.07098893434203</v>
+        <v>14.09986052839269</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.791550691530187</v>
+        <v>0.5890486225480862</v>
       </c>
       <c r="C3" t="n">
-        <v>20.34672117051515</v>
+        <v>26.96860943565988</v>
       </c>
       <c r="D3" t="n">
-        <v>72.69841749947631</v>
+        <v>52.44496236086461</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.09525488950772</v>
+        <v>2.986476516318797</v>
       </c>
       <c r="C4" t="n">
-        <v>62.56285420083224</v>
+        <v>66.6852128109646</v>
       </c>
       <c r="D4" t="n">
-        <v>165.6601076146068</v>
+        <v>128.4440156420187</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.56629816556373</v>
+        <v>9.621127501618743</v>
       </c>
       <c r="C5" t="n">
-        <v>145.0286796098601</v>
+        <v>156.686933597791</v>
       </c>
       <c r="D5" t="n">
-        <v>169.9896149903352</v>
+        <v>151.0418842983718</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.714583126634</v>
+        <v>14.04782790006761</v>
       </c>
       <c r="C6" t="n">
-        <v>273.9527698792555</v>
+        <v>255.1149949301677</v>
       </c>
       <c r="D6" t="n">
-        <v>103.6077622199829</v>
+        <v>107.7536827750172</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.46421209985527</v>
+        <v>9.941177253203202</v>
       </c>
       <c r="C7" t="n">
-        <v>348.0609770820301</v>
+        <v>318.5368783722158</v>
       </c>
       <c r="D7" t="n">
-        <v>52.99964981376406</v>
+        <v>58.38944471007905</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>279.5526587842793</v>
+        <v>250.3456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>139.7812381306608</v>
+        <v>121.9203021472986</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>24.62812290873548</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>50.96252332745193</v>
+        <v>48.11545498513618</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.880668748438394</v>
+        <v>3.273146845958866</v>
       </c>
       <c r="C2" t="n">
-        <v>8.749335540247575</v>
+        <v>14.54557398612074</v>
       </c>
       <c r="D2" t="n">
-        <v>8.411614329986671</v>
+        <v>11.59051339633784</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.343431770037137</v>
+        <v>0.3897538385859837</v>
       </c>
       <c r="C2" t="n">
-        <v>7.046003273379358</v>
+        <v>9.101782966072179</v>
       </c>
       <c r="D2" t="n">
-        <v>9.724211010564657</v>
+        <v>19.17942315016569</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.15894531709675</v>
+        <v>0.4368777283898306</v>
       </c>
       <c r="C3" t="n">
-        <v>31.27848185730338</v>
+        <v>29.43279617331937</v>
       </c>
       <c r="D3" t="n">
-        <v>77.72987448374121</v>
+        <v>51.31104376245955</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.5817030291954</v>
+        <v>2.105848825609408</v>
       </c>
       <c r="C4" t="n">
-        <v>89.01997308257953</v>
+        <v>66.83836545282711</v>
       </c>
       <c r="D4" t="n">
-        <v>169.1060420565131</v>
+        <v>125.7510816892697</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.88854809226815</v>
+        <v>7.485826244881931</v>
       </c>
       <c r="C5" t="n">
-        <v>225.875603054585</v>
+        <v>139.6290672365026</v>
       </c>
       <c r="D5" t="n">
-        <v>153.3244477107456</v>
+        <v>158.7976911619216</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.27425176685013</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="C6" t="n">
-        <v>280.2722798514922</v>
+        <v>253.545180351077</v>
       </c>
       <c r="D6" t="n">
-        <v>81.10708658635025</v>
+        <v>126.4707027564826</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>12.87562114119692</v>
       </c>
       <c r="C7" t="n">
-        <v>196.607740495579</v>
+        <v>343.5095947251419</v>
       </c>
       <c r="D7" t="n">
-        <v>32.39865598784899</v>
+        <v>71.2051792413169</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>102.9755166984479</v>
+        <v>323.6134957508761</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>38.82812170296133</v>
+        <v>202.4609203082984</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>86.83558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>36.25005223160922</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.600289815651307</v>
+        <v>2.73318560862312</v>
       </c>
       <c r="C2" t="n">
-        <v>7.3719435111893</v>
+        <v>8.843583319855268</v>
       </c>
       <c r="D2" t="n">
-        <v>20.25541863402019</v>
+        <v>24.16866498314798</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.49273953654066</v>
+        <v>5.286711387369074</v>
       </c>
       <c r="C3" t="n">
-        <v>22.04514469886213</v>
+        <v>28.71612034921921</v>
       </c>
       <c r="D3" t="n">
-        <v>10.20035864712436</v>
+        <v>10.926851948267</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39804628004896</v>
+        <v>11.67738562465652</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14271287790335</v>
+        <v>59.94391287323683</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576240738829289</v>
+        <v>0.7784923749771017</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.424736903040374</v>
+        <v>2.519164609097316</v>
       </c>
       <c r="C2" t="n">
-        <v>5.917975161199774</v>
+        <v>5.230751768227005</v>
       </c>
       <c r="D2" t="n">
-        <v>22.71175139004571</v>
+        <v>18.98601885242907</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.67775007329557</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C3" t="n">
-        <v>26.23720739599601</v>
+        <v>32.91309178487432</v>
       </c>
       <c r="D3" t="n">
-        <v>24.74985962406209</v>
+        <v>29.44752238888308</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.54950097693773</v>
+        <v>6.687665361329273</v>
       </c>
       <c r="C4" t="n">
-        <v>34.14027641518283</v>
+        <v>46.49458952542469</v>
       </c>
       <c r="D4" t="n">
-        <v>20.42035224833366</v>
+        <v>19.98641976305657</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43926885931322</v>
+        <v>13.62583935363348</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1348683730106</v>
+        <v>73.7398365020165</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250372391434362</v>
+        <v>1.60303992395688</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.330890034060181</v>
+        <v>1.778926840095221</v>
       </c>
       <c r="C2" t="n">
-        <v>7.03913103944963</v>
+        <v>4.975497365122835</v>
       </c>
       <c r="D2" t="n">
-        <v>22.1766988912312</v>
+        <v>20.53914372054752</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.78788574262046</v>
+        <v>8.497026380256143</v>
       </c>
       <c r="C3" t="n">
-        <v>24.54369260617026</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D3" t="n">
-        <v>37.17387682130548</v>
+        <v>38.27834298858314</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.84000048640355</v>
+        <v>12.02248238620644</v>
       </c>
       <c r="C4" t="n">
-        <v>52.07189823325082</v>
+        <v>68.77829891641879</v>
       </c>
       <c r="D4" t="n">
-        <v>28.23113698332128</v>
+        <v>30.78368101436299</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.7136327699962</v>
+        <v>6.651340696272142</v>
       </c>
       <c r="C5" t="n">
-        <v>38.28816046562561</v>
+        <v>53.55433726666352</v>
       </c>
       <c r="D5" t="n">
-        <v>30.01693605734623</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72955117224544</v>
+        <v>14.83277948987558</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0502621506972</v>
+        <v>87.34859032926728</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18238779306136</v>
+        <v>2.472129914979263</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.465389469541994</v>
+        <v>2.092104357749953</v>
       </c>
       <c r="C2" t="n">
-        <v>13.72385115766616</v>
+        <v>5.451645001682538</v>
       </c>
       <c r="D2" t="n">
-        <v>32.96806965631214</v>
+        <v>22.5144201014921</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5291052593268</v>
+        <v>7.176575718044184</v>
       </c>
       <c r="C3" t="n">
-        <v>26.13412388705009</v>
+        <v>21.56899706230243</v>
       </c>
       <c r="D3" t="n">
-        <v>45.75926049494383</v>
+        <v>45.82798283424111</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.67332436085984</v>
+        <v>14.6516027381794</v>
       </c>
       <c r="C4" t="n">
-        <v>57.29185077673112</v>
+        <v>65.16644911249479</v>
       </c>
       <c r="D4" t="n">
-        <v>39.84521232456105</v>
+        <v>43.03589236336318</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.48264432205772</v>
+        <v>12.56637061435918</v>
       </c>
       <c r="C5" t="n">
-        <v>69.53228115328035</v>
+        <v>95.49950793060849</v>
       </c>
       <c r="D5" t="n">
-        <v>32.98672286269284</v>
+        <v>31.88225669541517</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.47172192412398</v>
+        <v>6.963536466222627</v>
       </c>
       <c r="C6" t="n">
-        <v>37.19253002768617</v>
+        <v>51.24035792775378</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>33.77113927838603</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05050705411068</v>
+        <v>16.07025791520941</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7580698291982</v>
+        <v>100.6505627321011</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016835684703558</v>
+        <v>3.383212192675666</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.267477343911637</v>
+        <v>1.71118624850219</v>
       </c>
       <c r="C2" t="n">
-        <v>7.65174160689964</v>
+        <v>5.739297079026853</v>
       </c>
       <c r="D2" t="n">
-        <v>28.53744226704629</v>
+        <v>24.02925680914493</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.10557108816893</v>
+        <v>7.14712328691678</v>
       </c>
       <c r="C3" t="n">
-        <v>38.87230034965246</v>
+        <v>21.31865139771949</v>
       </c>
       <c r="D3" t="n">
-        <v>57.04445035526092</v>
+        <v>52.74439541065989</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.03670988015141</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="C4" t="n">
-        <v>51.15298238207581</v>
+        <v>58.9254789565978</v>
       </c>
       <c r="D4" t="n">
-        <v>46.30314872309656</v>
+        <v>55.60717171624359</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.64753687864217</v>
+        <v>17.40147805777472</v>
       </c>
       <c r="C5" t="n">
-        <v>66.1207078810227</v>
+        <v>108.9494514787898</v>
       </c>
       <c r="D5" t="n">
-        <v>31.73499453977815</v>
+        <v>39.39262663290327</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.92078153559227</v>
+        <v>11.91449013873929</v>
       </c>
       <c r="C6" t="n">
-        <v>50.59633143376788</v>
+        <v>103.2857489729899</v>
       </c>
       <c r="D6" t="n">
-        <v>31.11452999069417</v>
+        <v>36.46800022195202</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>23.83487076370406</v>
+        <v>46.35223610830891</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051358360375794</v>
+        <v>17.33232762539803</v>
       </c>
       <c r="C21" t="n">
-        <v>66.10648462852306</v>
+        <v>114.393362327627</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407098975234871</v>
+        <v>4.333081906349507</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.325981295538947</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C2" t="n">
-        <v>5.832563110930301</v>
+        <v>9.33543891968292</v>
       </c>
       <c r="D2" t="n">
-        <v>24.59376173908684</v>
+        <v>28.03773268558466</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.62022786937251</v>
+        <v>6.479534848028948</v>
       </c>
       <c r="C3" t="n">
-        <v>33.15361997241479</v>
+        <v>21.76043786463055</v>
       </c>
       <c r="D3" t="n">
-        <v>67.23008278682157</v>
+        <v>58.82141369994764</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.35876418487337</v>
+        <v>13.79650048778043</v>
       </c>
       <c r="C4" t="n">
-        <v>79.79252641036376</v>
+        <v>55.37744275344983</v>
       </c>
       <c r="D4" t="n">
-        <v>65.45999167606458</v>
+        <v>67.99977298695107</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.05973204570559</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="C5" t="n">
-        <v>82.66315669758144</v>
+        <v>108.8021893231528</v>
       </c>
       <c r="D5" t="n">
-        <v>41.45429681182157</v>
+        <v>48.81740459367266</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.37992066601029</v>
+        <v>17.50947030524187</v>
       </c>
       <c r="C6" t="n">
-        <v>82.71715282131501</v>
+        <v>137.6606630894878</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>40.53341746523807</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.13890945238431</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>52.52055693409162</v>
+        <v>95.75868932452963</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>26.45319189093031</v>
+        <v>42.05807164993335</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.269335870155833</v>
+        <v>17.72680972161419</v>
       </c>
       <c r="C21" t="n">
-        <v>75.41935965286677</v>
+        <v>127.6330299956222</v>
       </c>
       <c r="D21" t="n">
-        <v>5.452001902616875</v>
+        <v>5.318042916484257</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.911683764346792</v>
+        <v>1.347939597930871</v>
       </c>
       <c r="C2" t="n">
-        <v>5.465389469541994</v>
+        <v>5.824709129296326</v>
       </c>
       <c r="D2" t="n">
-        <v>25.97311726355361</v>
+        <v>21.98231284579033</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.91827826083604</v>
+        <v>8.98790023237955</v>
       </c>
       <c r="C3" t="n">
-        <v>26.89497835784137</v>
+        <v>36.26085145635594</v>
       </c>
       <c r="D3" t="n">
-        <v>71.95228924424873</v>
+        <v>65.98326320242812</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.89778473223387</v>
+        <v>9.227446672215772</v>
       </c>
       <c r="C4" t="n">
-        <v>81.69417171348984</v>
+        <v>88.86682044071702</v>
       </c>
       <c r="D4" t="n">
-        <v>82.77900292668257</v>
+        <v>63.16270204812704</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.12831551628263</v>
+        <v>9.842020735074275</v>
       </c>
       <c r="C5" t="n">
-        <v>118.9878217547134</v>
+        <v>82.24591392327655</v>
       </c>
       <c r="D5" t="n">
-        <v>55.59146375297565</v>
+        <v>38.72994693253668</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.5975498611836</v>
+        <v>6.601271563355554</v>
       </c>
       <c r="C6" t="n">
-        <v>109.1624907306114</v>
+        <v>63.07434475474484</v>
       </c>
       <c r="D6" t="n">
-        <v>39.56737772425921</v>
+        <v>25.96231803880691</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.16371518689774</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>87.91354341989337</v>
+        <v>29.52409870981433</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>49.73533869714341</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>28.84374755077128</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.47333480342644</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.07501653854744</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.539167952998135</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
